--- a/artfynd/A 7107-2023 artfynd.xlsx
+++ b/artfynd/A 7107-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ3"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -880,6 +880,113 @@
       <c r="AZ3" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/121462276</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>137091132</v>
+      </c>
+      <c r="B4" t="n">
+        <v>102471</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>221223</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Vippärt</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lathyrus niger</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Grötsjö, V om vägskäl mot Boningamålen, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>550060</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6271875</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Karlslunda</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>vägkant</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Tomas Burén</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Tomas Burén, Pontus Axén</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137091132</t>
         </is>
       </c>
     </row>
@@ -887,6 +994,7 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 7107-2023 artfynd.xlsx
+++ b/artfynd/A 7107-2023 artfynd.xlsx
@@ -888,7 +888,7 @@
         <v>137091132</v>
       </c>
       <c r="B4" t="n">
-        <v>102471</v>
+        <v>102472</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 7107-2023 artfynd.xlsx
+++ b/artfynd/A 7107-2023 artfynd.xlsx
@@ -888,7 +888,7 @@
         <v>137091132</v>
       </c>
       <c r="B4" t="n">
-        <v>102472</v>
+        <v>102478</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 7107-2023 artfynd.xlsx
+++ b/artfynd/A 7107-2023 artfynd.xlsx
@@ -888,7 +888,7 @@
         <v>137091132</v>
       </c>
       <c r="B4" t="n">
-        <v>102478</v>
+        <v>102482</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 7107-2023 artfynd.xlsx
+++ b/artfynd/A 7107-2023 artfynd.xlsx
@@ -888,7 +888,7 @@
         <v>137091132</v>
       </c>
       <c r="B4" t="n">
-        <v>102504</v>
+        <v>102519</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 7107-2023 artfynd.xlsx
+++ b/artfynd/A 7107-2023 artfynd.xlsx
@@ -888,7 +888,7 @@
         <v>137091132</v>
       </c>
       <c r="B4" t="n">
-        <v>102519</v>
+        <v>102520</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 7107-2023 artfynd.xlsx
+++ b/artfynd/A 7107-2023 artfynd.xlsx
@@ -888,7 +888,7 @@
         <v>137091132</v>
       </c>
       <c r="B4" t="n">
-        <v>102520</v>
+        <v>102525</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 7107-2023 artfynd.xlsx
+++ b/artfynd/A 7107-2023 artfynd.xlsx
@@ -888,7 +888,7 @@
         <v>137091132</v>
       </c>
       <c r="B4" t="n">
-        <v>102525</v>
+        <v>102528</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 7107-2023 artfynd.xlsx
+++ b/artfynd/A 7107-2023 artfynd.xlsx
@@ -888,7 +888,7 @@
         <v>137091132</v>
       </c>
       <c r="B4" t="n">
-        <v>102528</v>
+        <v>102534</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 7107-2023 artfynd.xlsx
+++ b/artfynd/A 7107-2023 artfynd.xlsx
@@ -888,7 +888,7 @@
         <v>137091132</v>
       </c>
       <c r="B4" t="n">
-        <v>102534</v>
+        <v>102546</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 7107-2023 artfynd.xlsx
+++ b/artfynd/A 7107-2023 artfynd.xlsx
@@ -888,7 +888,7 @@
         <v>137091132</v>
       </c>
       <c r="B4" t="n">
-        <v>102546</v>
+        <v>102547</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 7107-2023 artfynd.xlsx
+++ b/artfynd/A 7107-2023 artfynd.xlsx
@@ -888,7 +888,7 @@
         <v>137091132</v>
       </c>
       <c r="B4" t="n">
-        <v>102547</v>
+        <v>102550</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 7107-2023 artfynd.xlsx
+++ b/artfynd/A 7107-2023 artfynd.xlsx
@@ -888,7 +888,7 @@
         <v>137091132</v>
       </c>
       <c r="B4" t="n">
-        <v>102550</v>
+        <v>102554</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
